--- a/docs/sitemap_document.xlsx
+++ b/docs/sitemap_document.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">関連資料</t>
   </si>
   <si>
-    <t xml:space="preserve">docs/11-sitemap-to-url-design.html</t>
+    <t xml:space="preserve">docs/sitemap-to-url-design.html</t>
   </si>
   <si>
     <t xml:space="preserve">階層</t>
@@ -111,10 +111,10 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">サービス全体の価値を短時間で伝え、各ページへ誘導する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キャッチコピー、課題提起、特徴、CTA（無料相談/申込み）</t>
+    <t xml:space="preserve">サービス全体の価値を短時間で伝え、主要導線へ誘導する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キャッチコピー、課題提起、特徴、CTA（無料相談/申込み）、運営者情報（About）</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -171,7 +171,7 @@
     <t xml:space="preserve">お問い合わせ（f_contact）</t>
   </si>
   <si>
-    <t xml:space="preserve">問い合わせ・相談を受け付ける</t>
+    <t xml:space="preserve">導入相談・機能質問を受け付ける</t>
   </si>
   <si>
     <t xml:space="preserve">フォーム、連絡先、返信目安</t>
@@ -195,22 +195,22 @@
     <t xml:space="preserve">Webアプリ紹介（webapp）</t>
   </si>
   <si>
-    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+    <t xml:space="preserve">Webアプリの機能と主要画面を案内する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">機能概要、主要画面導線、ログイン導線</t>
   </si>
   <si>
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+    <t xml:space="preserve">LINE友だち追加（line-qr）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINE Bot への友だち追加QRコードを提供する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINEチャンネルQRコード表示、友だち追加ボタン</t>
   </si>
   <si>
     <t xml:space="preserve">画面名</t>
@@ -591,25 +591,25 @@
     <t xml:space="preserve">ログインフォーム表示</t>
   </si>
   <si>
-    <t xml:space="preserve">/app/sessions</t>
+    <t xml:space="preserve">/app/login</t>
   </si>
   <si>
     <t xml:space="preserve">ログイン処理</t>
   </si>
   <si>
-    <t xml:space="preserve">認証してセッション作成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/app/sessions/current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELETE</t>
+    <t xml:space="preserve">Spring Security が認証・セッション作成（公開）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/app/logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST</t>
   </si>
   <si>
     <t xml:space="preserve">ログアウト</t>
   </si>
   <si>
-    <t xml:space="preserve">現在セッション削除</t>
+    <t xml:space="preserve">Spring Security がセッション破棄（全ユーザー）</t>
   </si>
   <si>
     <t xml:space="preserve">/app/dashboard</t>
@@ -621,13 +621,13 @@
     <t xml:space="preserve">KPI・通知・予定表示</t>
   </si>
   <si>
-    <t xml:space="preserve">/app/users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユーザー一覧/検索</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧、条件検索</t>
+    <t xml:space="preserve">/app/admin/users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザー一覧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザー一覧閲覧（VET/STAFF/ADMIN/SUPER）</t>
   </si>
   <si>
     <t xml:space="preserve">/app/pets</t>
@@ -645,13 +645,13 @@
     <t xml:space="preserve">体重/食事/運動履歴表示</t>
   </si>
   <si>
-    <t xml:space="preserve">/app/symptom-checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI症状チェック実行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入力症状を診断ロジックへ送信</t>
+    <t xml:space="preserve">/app/pets/{id}/symptom-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI症状チェック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">症状入力 → AI/フォールバック判定・保存（Standard+：OpenAI / Light：keyword）</t>
   </si>
   <si>
     <t xml:space="preserve">/app/appointments</t>
@@ -672,13 +672,13 @@
     <t xml:space="preserve">履歴検索・一覧表示</t>
   </si>
   <si>
-    <t xml:space="preserve">/app/billings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">請求一覧/検索</t>
-  </si>
-  <si>
-    <t xml:space="preserve">請求状態確認</t>
+    <t xml:space="preserve">/app/admin/billing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請求一覧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNPAID/PARTIAL/PAID 各ステータスの請求一覧（ADMIN/SUPER のみ）</t>
   </si>
   <si>
     <t xml:space="preserve">/app/notifications</t>
@@ -690,13 +690,13 @@
     <t xml:space="preserve">配信履歴表示</t>
   </si>
   <si>
-    <t xml:space="preserve">/app/reports/monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次集計表示</t>
+    <t xml:space="preserve">/app/reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サービス統計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザー・ペット・予約・サブスク集計（ADMIN/SUPER のみ）</t>
   </si>
 </sst>
 </file>
